--- a/AAII_Financials/Yearly/NCNC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NCNC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>NCNC</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1068,8 +1068,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-16800</v>
       </c>
       <c r="E23" s="3">
         <v>-1100</v>
@@ -1149,8 +1149,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-16800</v>
       </c>
       <c r="E26" s="3">
         <v>-1100</v>
@@ -1176,8 +1176,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-16800</v>
       </c>
       <c r="E27" s="3">
         <v>-1100</v>
@@ -1338,8 +1338,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-16800</v>
       </c>
       <c r="E33" s="3">
         <v>-1100</v>
@@ -1392,8 +1392,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-16800</v>
       </c>
       <c r="E35" s="3">
         <v>-1100</v>
@@ -1586,7 +1586,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -1881,8 +1881,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>3600</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3">
         <v>1000</v>
@@ -2017,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -2272,8 +2272,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-19100</v>
       </c>
       <c r="E72" s="3">
         <v>-2400</v>
@@ -2380,8 +2380,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>-3700</v>
       </c>
       <c r="E76" s="3">
         <v>-800</v>
@@ -2466,8 +2466,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-16800</v>
       </c>
       <c r="E81" s="3">
         <v>-1100</v>
@@ -2964,8 +2964,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -2991,8 +2991,8 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
